--- a/Data/testDataPoland5.xlsx
+++ b/Data/testDataPoland5.xlsx
@@ -1,20 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{6BE09BF7-166C-4551-A9A0-75E7F910E6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="155">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -238,24 +253,12 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>Test failed for 'Ryann Schneider' Employee: undefined&amp; find failed Screenshot Path:-&gt;H:\GKALE\WorkDaySuite_Playwright/WorkdayFailedScreenshot/2025-03-03T08-49-30-042Z.png</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>766 Recruitment (Gybop Sytavu (10223416))</t>
   </si>
   <si>
     <t>Poland</t>
   </si>
   <si>
-    <t>Ryann</t>
-  </si>
-  <si>
-    <t>Schneider</t>
-  </si>
-  <si>
     <t xml:space="preserve">698 980 460 </t>
   </si>
   <si>
@@ -301,7 +304,7 @@
     <t>Full time</t>
   </si>
   <si>
-    <t>Za</t>
+    <t>ZasadniczaSzkołaZawodowa</t>
   </si>
   <si>
     <t xml:space="preserve">RE029_NEW2 </t>
@@ -352,9 +355,6 @@
     <t>ID Card</t>
   </si>
   <si>
-    <t>GHE456902</t>
-  </si>
-  <si>
     <t>Male</t>
   </si>
   <si>
@@ -397,231 +397,210 @@
     <t>765 Store Management (Kires Pivyba (10226524))</t>
   </si>
   <si>
+    <t>Auto 91546437</t>
+  </si>
+  <si>
+    <t>Fixed Term (Fixed Term)</t>
+  </si>
+  <si>
+    <t>Team Manager - Retail_NEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 Retail Management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">251 Management Retail </t>
+  </si>
+  <si>
+    <t>Single (Poland)</t>
+  </si>
+  <si>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t>Test_4</t>
+  </si>
+  <si>
     <t>Auto 14500870</t>
   </si>
   <si>
-    <t>Fixed Term (Fixed Term)</t>
-  </si>
-  <si>
-    <t>Team Manager - Retail_NEW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 Retail Management </t>
-  </si>
-  <si>
-    <t xml:space="preserve">251 Management Retail </t>
-  </si>
-  <si>
-    <t>GHE456898</t>
-  </si>
-  <si>
-    <t>Single (Poland)</t>
-  </si>
-  <si>
-    <t>Test_3</t>
-  </si>
-  <si>
-    <t>GHE456899</t>
-  </si>
-  <si>
-    <t>Test_4</t>
-  </si>
-  <si>
-    <t>GHE456900</t>
-  </si>
-  <si>
     <t>Test_5</t>
   </si>
   <si>
-    <t>GHE456901</t>
-  </si>
-  <si>
     <t>Test_6</t>
   </si>
   <si>
     <t>Test_7</t>
   </si>
   <si>
-    <t>GHE456903</t>
-  </si>
-  <si>
     <t>Test_8</t>
   </si>
   <si>
-    <t>GHE456904</t>
-  </si>
-  <si>
     <t>Test_9</t>
   </si>
   <si>
-    <t>GHE456905</t>
-  </si>
-  <si>
     <t>Test_10</t>
   </si>
   <si>
-    <t>GHE456906</t>
-  </si>
-  <si>
     <t>Test_11</t>
   </si>
   <si>
-    <t>GHE456907</t>
-  </si>
-  <si>
     <t>Test_12</t>
   </si>
   <si>
-    <t>GHE456908</t>
-  </si>
-  <si>
     <t>Test_13</t>
   </si>
   <si>
-    <t>GHE456909</t>
-  </si>
-  <si>
     <t>Test_14</t>
   </si>
   <si>
-    <t>GHE456910</t>
-  </si>
-  <si>
-    <t>Test_15</t>
-  </si>
-  <si>
-    <t>GHE456911</t>
-  </si>
-  <si>
-    <t>Test_16</t>
-  </si>
-  <si>
-    <t>GHE456912</t>
-  </si>
-  <si>
-    <t>Test_17</t>
-  </si>
-  <si>
-    <t>GHE456913</t>
-  </si>
-  <si>
-    <t>Test_18</t>
-  </si>
-  <si>
-    <t>GHE456914</t>
-  </si>
-  <si>
-    <t>Test_19</t>
-  </si>
-  <si>
-    <t>GHE456915</t>
-  </si>
-  <si>
-    <t>Test_20</t>
-  </si>
-  <si>
-    <t>GHE456916</t>
+    <t>GSK476930</t>
+  </si>
+  <si>
+    <t>GSK476931</t>
+  </si>
+  <si>
+    <t>GSK476932</t>
+  </si>
+  <si>
+    <t>GSK476933</t>
+  </si>
+  <si>
+    <t>GSK476934</t>
+  </si>
+  <si>
+    <t>GSK476935</t>
+  </si>
+  <si>
+    <t>GSK476936</t>
+  </si>
+  <si>
+    <t>GSK476937</t>
+  </si>
+  <si>
+    <t>GSK476938</t>
+  </si>
+  <si>
+    <t>GSK476939</t>
+  </si>
+  <si>
+    <t>GSK476940</t>
+  </si>
+  <si>
+    <t>GSK476941</t>
+  </si>
+  <si>
+    <t>GSK476942</t>
+  </si>
+  <si>
+    <t>GSK476943</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color indexed="63"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color indexed="12"/>
+      <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="8"/>
-      <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color indexed="10"/>
-      <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
-    </font>
-    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FFFF0000"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,7 +609,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -641,7 +620,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -655,10 +640,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -668,8 +661,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -760,7 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -769,11 +766,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1107,9 +1104,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BX23"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BX15"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
     <col min="2" max="2" width="34.1796875" customWidth="1"/>
@@ -1174,7 +1171,7 @@
     <col min="76" max="76" width="26.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" customHeight="1" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:76" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1404,95 +1401,87 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D2" s="29" t="s">
+      <c r="E2" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="I2" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="J2" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="K2" s="35">
+        <f t="shared" ref="K2:K14" ca="1" si="0">TODAY()-31</f>
+        <v>45688</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="N2" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="O2" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="P2" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="35">
-        <f t="shared" ref="K2:K4" si="0">TODAY()-31</f>
-        <v>45688</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="30" t="s">
+      <c r="Q2" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="R2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U2" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="V2" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="W2" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X2" s="39">
+        <f t="shared" ref="X2" ca="1" si="1">K2</f>
+        <v>45688</v>
+      </c>
+      <c r="Y2" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="Z2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="R2" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="S2" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="37" t="s">
+      <c r="AA2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="V2" s="38" t="s">
+      <c r="AB2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="W2" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="X2" s="39">
-        <f t="shared" ref="X2" si="1">K2</f>
-        <v>45688</v>
-      </c>
-      <c r="Y2" s="34" t="s">
+      <c r="AC2" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB2" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="AD2" s="40">
         <v>766</v>
@@ -1504,10 +1493,10 @@
         <v>40</v>
       </c>
       <c r="AG2" s="41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AH2" s="41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AI2" s="18">
         <v>43831</v>
@@ -1516,210 +1505,210 @@
         <v>45292</v>
       </c>
       <c r="AK2" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AL2" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AM2" s="18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AN2" s="34">
         <v>110</v>
       </c>
       <c r="AO2" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP2" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ2" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR2" s="42">
+        <f t="shared" ref="AR2" ca="1" si="2">X2</f>
+        <v>45688</v>
+      </c>
+      <c r="AS2" s="42">
+        <f t="shared" ref="AS2" ca="1" si="3">X2</f>
+        <v>45688</v>
+      </c>
+      <c r="AT2" s="20" t="str">
+        <f t="shared" ref="AT2:AT3" si="4">AM2</f>
+        <v>N/A</v>
+      </c>
+      <c r="AU2" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AP2" s="14" t="s">
+      <c r="AW2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AQ2" s="34" t="s">
+      <c r="AX2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AR2" s="42">
-        <f t="shared" ref="AR2" si="2">X2</f>
-        <v>45688</v>
-      </c>
-      <c r="AS2" s="42">
-        <f t="shared" ref="AS2" si="3">X2</f>
-        <v>45688</v>
-      </c>
-      <c r="AT2" s="20">
-        <f t="shared" ref="AT2:AT3" si="4">AM2</f>
-        <v>NaN</v>
-      </c>
-      <c r="AU2" s="6" t="s">
+      <c r="AY2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="BB2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD2" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="BE2" s="15">
+        <v>9577896572</v>
+      </c>
+      <c r="BF2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG2" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BH2" s="15">
+        <v>49678965402</v>
+      </c>
+      <c r="BI2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ2" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BK2" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="BL2" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="BC2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BD2" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE2" s="15">
-        <v>9477896538</v>
-      </c>
-      <c r="BF2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG2" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH2" s="15">
-        <v>47678965283</v>
-      </c>
-      <c r="BI2" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ2" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK2" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="BL2" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="BM2" s="44">
         <v>35591</v>
       </c>
       <c r="BN2" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO2" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP2" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ2" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR2" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="BO2" s="24" t="s">
+      <c r="BT2" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="BP2" s="46" t="s">
+      <c r="BU2" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="BQ2" s="30" t="s">
+      <c r="BV2" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR2" s="47" t="s">
+      <c r="BW2" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="BS2" s="30" t="s">
+      <c r="BX2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT2" s="46" t="s">
+    </row>
+    <row r="3" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
         <v>120</v>
-      </c>
-      <c r="BU2" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV2" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW2" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX2" s="30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
-        <v>125</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="1"/>
       <c r="D3" s="29" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="32"/>
       <c r="H3" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K3" s="35">
+        <f t="shared" ref="K3:K15" ca="1" si="5">TODAY()-31</f>
+        <v>45688</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M3" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N3" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="34" t="s">
+      <c r="O3" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="J3" s="34" t="s">
+      <c r="P3" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K3" s="35">
-        <f t="shared" ref="K3" si="5">TODAY()-31</f>
-        <v>45688</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="M3" s="30" t="s">
+      <c r="Q3" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="N3" s="34" t="s">
+      <c r="R3" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T3" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U3" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="V3" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="P3" s="34" t="s">
+      <c r="W3" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X3" s="39">
+        <f t="shared" ref="X3:X4" ca="1" si="6">K3</f>
+        <v>45688</v>
+      </c>
+      <c r="Y3" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="Q3" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="T3" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="U3" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="V3" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="W3" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="X3" s="39">
-        <f t="shared" ref="X3:X4" si="6">K3</f>
-        <v>45688</v>
-      </c>
-      <c r="Y3" s="34" t="s">
+      <c r="Z3" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC3" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC3" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="AD3" s="40">
         <v>765</v>
@@ -1731,10 +1720,10 @@
         <v>40</v>
       </c>
       <c r="AG3" s="41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AH3" s="41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AI3" s="18">
         <v>43831</v>
@@ -1743,214 +1732,214 @@
         <v>45292</v>
       </c>
       <c r="AK3" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AL3" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AM3" s="18">
-        <f>TODAY()+365</f>
+        <f ca="1">TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN3" s="34">
         <v>110</v>
       </c>
       <c r="AO3" s="34" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AP3" s="14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AQ3" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR3" s="42">
+        <f t="shared" ref="AR3:AR4" ca="1" si="7">X3</f>
+        <v>45688</v>
+      </c>
+      <c r="AS3" s="42">
+        <f t="shared" ref="AS3:AS4" ca="1" si="8">X3</f>
+        <v>45688</v>
+      </c>
+      <c r="AT3" s="20">
+        <f t="shared" ca="1" si="4"/>
+        <v>46084</v>
+      </c>
+      <c r="AU3" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX3" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AR3" s="42">
-        <f t="shared" ref="AR3:AR4" si="7">X3</f>
-        <v>45688</v>
-      </c>
-      <c r="AS3" s="42">
-        <f t="shared" ref="AS3:AS4" si="8">X3</f>
-        <v>45688</v>
-      </c>
-      <c r="AT3" s="20">
-        <f t="shared" si="4"/>
-        <v>46084</v>
-      </c>
-      <c r="AU3" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AV3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="AW3" s="2" t="s">
+      <c r="AY3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AX3" s="2" t="s">
+      <c r="BB3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD3" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="AY3" s="2" t="s">
+      <c r="BE3" s="15">
+        <v>9577896573</v>
+      </c>
+      <c r="BF3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG3" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="AZ3" s="2" t="s">
+      <c r="BH3" s="15">
+        <v>49678965403</v>
+      </c>
+      <c r="BI3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ3" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="BA3" s="2" t="s">
+      <c r="BK3" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="BL3" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="BC3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BD3" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE3" s="15">
-        <v>9477896534</v>
-      </c>
-      <c r="BF3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG3" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH3" s="15">
-        <v>47678965279</v>
-      </c>
-      <c r="BI3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ3" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK3" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="BL3" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="BM3" s="44">
         <v>35591</v>
       </c>
       <c r="BN3" s="45" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="BO3" s="24" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="BP3" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ3" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR3" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS3" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT3" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU3" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="BQ3" s="30" t="s">
+      <c r="BV3" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR3" s="47" t="s">
+      <c r="BW3" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="BS3" s="30" t="s">
+      <c r="BX3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT3" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU3" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="BV3" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW3" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="BX3" s="30" t="s">
-        <v>124</v>
-      </c>
     </row>
-    <row r="4" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="27" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B4" s="28"/>
       <c r="C4" s="1"/>
       <c r="D4" s="29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F4" s="31"/>
       <c r="G4" s="32"/>
       <c r="H4" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K4" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="O4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="P4" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="35">
-        <f t="shared" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>77</v>
-      </c>
-      <c r="M4" s="30" t="s">
+      <c r="Q4" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="34" t="s">
+      <c r="R4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S4" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T4" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U4" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="V4" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="P4" s="34" t="s">
+      <c r="W4" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X4" s="39">
+        <f t="shared" ca="1" si="6"/>
+        <v>45688</v>
+      </c>
+      <c r="Y4" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="Q4" s="34" t="s">
+      <c r="Z4" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="R4" s="34" t="s">
-        <v>87</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="U4" s="37" t="s">
+      <c r="AA4" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="V4" s="38" t="s">
+      <c r="AB4" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="W4" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="X4" s="39">
-        <f t="shared" si="6"/>
-        <v>45688</v>
-      </c>
-      <c r="Y4" s="34" t="s">
+      <c r="AC4" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="Z4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>94</v>
-      </c>
       <c r="AD4" s="40">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AE4" s="40" t="s">
         <v>70</v>
@@ -1959,10 +1948,10 @@
         <v>40</v>
       </c>
       <c r="AG4" s="41" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="AI4" s="18">
         <v>43831</v>
@@ -1971,379 +1960,2635 @@
         <v>45292</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AM4" s="18" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AN4" s="34">
         <v>110</v>
       </c>
       <c r="AO4" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ4" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR4" s="42">
+        <f t="shared" ca="1" si="7"/>
+        <v>45688</v>
+      </c>
+      <c r="AS4" s="42">
+        <f t="shared" ca="1" si="8"/>
+        <v>45688</v>
+      </c>
+      <c r="AT4" s="20" t="str">
+        <f t="shared" ref="AT4:AT5" si="9">AM4</f>
+        <v>N/A</v>
+      </c>
+      <c r="AU4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV4" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AP4" s="14" t="s">
+      <c r="AW4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AQ4" s="34" t="s">
+      <c r="AX4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AR4" s="42">
-        <f t="shared" si="7"/>
-        <v>45688</v>
-      </c>
-      <c r="AS4" s="42">
-        <f t="shared" si="8"/>
-        <v>45688</v>
-      </c>
-      <c r="AT4" s="20">
-        <f t="shared" ref="AT4" si="9">AM4</f>
-        <v>NaN</v>
-      </c>
-      <c r="AU4" s="6" t="s">
+      <c r="AY4" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AV4" s="2" t="s">
+      <c r="AZ4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AW4" s="2" t="s">
+      <c r="BA4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AX4" s="2" t="s">
+      <c r="BB4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD4" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="AY4" s="2" t="s">
+      <c r="BE4" s="15">
+        <v>9577896574</v>
+      </c>
+      <c r="BF4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG4" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="AZ4" s="2" t="s">
+      <c r="BH4" s="15">
+        <v>49678965404</v>
+      </c>
+      <c r="BI4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ4" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="BA4" s="2" t="s">
+      <c r="BK4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="BL4" s="14" t="s">
         <v>108</v>
-      </c>
-      <c r="BB4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="BC4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BD4" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="BE4" s="15">
-        <v>9477896535</v>
-      </c>
-      <c r="BF4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG4" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="BH4" s="15">
-        <v>47678965280</v>
-      </c>
-      <c r="BI4" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="BJ4" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="BK4" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="BL4" s="14" t="s">
-        <v>113</v>
       </c>
       <c r="BM4" s="44">
         <v>35591</v>
       </c>
       <c r="BN4" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO4" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP4" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ4" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR4" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS4" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="BO4" s="24" t="s">
+      <c r="BT4" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="BP4" s="46" t="s">
+      <c r="BU4" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="BQ4" s="30" t="s">
+      <c r="BV4" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="BR4" s="47" t="s">
+      <c r="BW4" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="BS4" s="30" t="s">
+      <c r="BX4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="BT4" s="46" t="s">
-        <v>120</v>
-      </c>
-      <c r="BU4" s="46" t="s">
+    </row>
+    <row r="5" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="28"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="BV4" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW4" s="30" t="s">
+      <c r="E5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L5" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U5" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V5" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="39">
+        <f t="shared" ref="X5:X6" ca="1" si="10">K5</f>
+        <v>45688</v>
+      </c>
+      <c r="Y5" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA5" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="BX4" s="30" t="s">
+      <c r="AB5" s="6" t="s">
         <v>124</v>
       </c>
+      <c r="AC5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD5" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE5" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF5" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG5" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH5" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI5" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ5" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL5" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM5" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN5" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO5" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP5" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ5" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR5" s="42">
+        <f t="shared" ref="AR5:AR6" ca="1" si="11">X5</f>
+        <v>45688</v>
+      </c>
+      <c r="AS5" s="42">
+        <f t="shared" ref="AS5:AS6" ca="1" si="12">X5</f>
+        <v>45688</v>
+      </c>
+      <c r="AT5" s="20">
+        <f t="shared" ca="1" si="9"/>
+        <v>46084</v>
+      </c>
+      <c r="AU5" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD5" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE5" s="15">
+        <v>9577896575</v>
+      </c>
+      <c r="BF5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG5" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH5" s="15">
+        <v>49678965405</v>
+      </c>
+      <c r="BI5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ5" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK5" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="BL5" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM5" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN5" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO5" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP5" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR5" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS5" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT5" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV5" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW5" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX5" s="30" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="5" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+    <row r="6" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="28"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U6" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V6" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X6" s="39">
+        <f t="shared" ca="1" si="10"/>
+        <v>45688</v>
+      </c>
+      <c r="Y6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC6" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD6" s="40">
+        <v>766</v>
+      </c>
+      <c r="AE6" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF6" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG6" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH6" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI6" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ6" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK6" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL6" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM6" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN6" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO6" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ6" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR6" s="42">
+        <f t="shared" ca="1" si="11"/>
+        <v>45688</v>
+      </c>
+      <c r="AS6" s="42">
+        <f t="shared" ca="1" si="12"/>
+        <v>45688</v>
+      </c>
+      <c r="AT6" s="20" t="str">
+        <f t="shared" ref="AT6:AT15" si="13">AM6</f>
+        <v>N/A</v>
+      </c>
+      <c r="AU6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD6" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE6" s="15">
+        <v>9577896576</v>
+      </c>
+      <c r="BF6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG6" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH6" s="15">
+        <v>49678965406</v>
+      </c>
+      <c r="BI6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ6" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK6" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM6" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN6" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO6" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP6" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ6" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR6" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS6" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT6" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU6" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV6" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW6" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX6" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K7" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U7" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V7" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X7" s="39">
+        <f t="shared" ref="X7:X15" ca="1" si="14">K7</f>
+        <v>45688</v>
+      </c>
+      <c r="Y7" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC7" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD7" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE7" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF7" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG7" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH7" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI7" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ7" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK7" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL7" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM7" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN7" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO7" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP7" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ7" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR7" s="42">
+        <f t="shared" ref="AR7:AR15" ca="1" si="15">X7</f>
+        <v>45688</v>
+      </c>
+      <c r="AS7" s="42">
+        <f t="shared" ref="AS7:AS15" ca="1" si="16">X7</f>
+        <v>45688</v>
+      </c>
+      <c r="AT7" s="20">
+        <f t="shared" ca="1" si="13"/>
+        <v>46084</v>
+      </c>
+      <c r="AU7" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD7" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE7" s="15">
+        <v>9577896577</v>
+      </c>
+      <c r="BF7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG7" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH7" s="15">
+        <v>49678965407</v>
+      </c>
+      <c r="BI7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ7" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK7" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="BL7" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM7" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN7" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO7" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP7" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ7" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR7" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS7" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT7" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV7" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW7" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX7" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V8" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X8" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y8" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD8" s="40">
+        <v>766</v>
+      </c>
+      <c r="AE8" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF8" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG8" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH8" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI8" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ8" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK8" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL8" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM8" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN8" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO8" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP8" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ8" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR8" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS8" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT8" s="20" t="str">
+        <f t="shared" si="13"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD8" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE8" s="15">
+        <v>9577896578</v>
+      </c>
+      <c r="BF8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG8" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH8" s="15">
+        <v>49678965408</v>
+      </c>
+      <c r="BI8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ8" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK8" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="BL8" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM8" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN8" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO8" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP8" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ8" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR8" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS8" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT8" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU8" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV8" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW8" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX8" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L9" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U9" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V9" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X9" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y9" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA9" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC9" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD9" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE9" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF9" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG9" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH9" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI9" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ9" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK9" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL9" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM9" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN9" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO9" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP9" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ9" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR9" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS9" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT9" s="20">
+        <f t="shared" ca="1" si="13"/>
+        <v>46084</v>
+      </c>
+      <c r="AU9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV9" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD9" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE9" s="15">
+        <v>9577896579</v>
+      </c>
+      <c r="BF9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG9" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH9" s="15">
+        <v>49678965409</v>
+      </c>
+      <c r="BI9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ9" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK9" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="BL9" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM9" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN9" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO9" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP9" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ9" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR9" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS9" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT9" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU9" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV9" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW9" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX9" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="28"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L10" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R10" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T10" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U10" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V10" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X10" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC10" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD10" s="40">
+        <v>766</v>
+      </c>
+      <c r="AE10" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF10" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG10" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH10" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI10" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ10" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK10" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM10" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN10" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO10" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP10" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ10" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR10" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS10" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT10" s="20" t="str">
+        <f t="shared" si="13"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD10" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE10" s="15">
+        <v>9577896580</v>
+      </c>
+      <c r="BF10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG10" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH10" s="15">
+        <v>49678965410</v>
+      </c>
+      <c r="BI10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ10" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK10" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="BL10" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM10" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN10" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO10" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP10" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ10" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR10" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS10" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT10" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU10" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV10" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW10" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX10" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="BE5" s="15">
-        <v>9477896536</v>
-      </c>
-      <c r="BH5" s="15">
-        <v>47678965281</v>
-      </c>
-      <c r="BK5" s="15" t="s">
+      <c r="B11" s="28"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L11" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T11" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U11" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V11" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W11" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X11" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y11" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z11" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB11" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC11" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD11" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE11" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF11" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG11" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH11" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI11" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ11" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK11" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL11" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM11" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN11" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO11" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP11" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ11" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR11" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS11" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT11" s="20">
+        <f t="shared" ca="1" si="13"/>
+        <v>46084</v>
+      </c>
+      <c r="AU11" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV11" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD11" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE11" s="15">
+        <v>9577896581</v>
+      </c>
+      <c r="BF11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG11" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH11" s="15">
+        <v>49678965411</v>
+      </c>
+      <c r="BI11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ11" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK11" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="BL11" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM11" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN11" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO11" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP11" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ11" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR11" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS11" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT11" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU11" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV11" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW11" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX11" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="27" t="s">
         <v>137</v>
       </c>
+      <c r="B12" s="28"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L12" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M12" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U12" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V12" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W12" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X12" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y12" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC12" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD12" s="40">
+        <v>766</v>
+      </c>
+      <c r="AE12" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF12" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG12" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH12" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI12" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ12" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK12" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL12" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM12" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN12" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO12" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP12" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ12" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR12" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS12" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT12" s="20" t="str">
+        <f t="shared" si="13"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU12" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD12" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE12" s="15">
+        <v>9577896582</v>
+      </c>
+      <c r="BF12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG12" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH12" s="15">
+        <v>49678965412</v>
+      </c>
+      <c r="BI12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ12" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK12" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="BL12" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM12" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN12" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO12" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP12" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ12" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR12" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS12" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT12" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU12" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV12" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW12" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX12" s="30" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="6" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+    <row r="13" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="BE6" s="15">
-        <v>9477896537</v>
-      </c>
-      <c r="BH6" s="15">
-        <v>47678965282</v>
-      </c>
-      <c r="BK6" s="15" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="7" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="BE7" s="15">
-        <v>9477896538</v>
-      </c>
-      <c r="BH7" s="15">
-        <v>47678965283</v>
-      </c>
-      <c r="BK7" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="BE8" s="15">
-        <v>9477896539</v>
-      </c>
-      <c r="BH8" s="15">
-        <v>47678965284</v>
-      </c>
-      <c r="BK8" s="15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="BE9" s="15">
-        <v>9477896540</v>
-      </c>
-      <c r="BH9" s="15">
-        <v>47678965285</v>
-      </c>
-      <c r="BK9" s="15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="BE10" s="15">
-        <v>9477896541</v>
-      </c>
-      <c r="BH10" s="15">
-        <v>47678965286</v>
-      </c>
-      <c r="BK10" s="15" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="BE11" s="15">
-        <v>9477896542</v>
-      </c>
-      <c r="BH11" s="15">
-        <v>47678965287</v>
-      </c>
-      <c r="BK11" s="15" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="BE12" s="15">
-        <v>9477896543</v>
-      </c>
-      <c r="BH12" s="15">
-        <v>47678965288</v>
-      </c>
-      <c r="BK12" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>151</v>
+      <c r="B13" s="28"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K13" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L13" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M13" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O13" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U13" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V13" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X13" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y13" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z13" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA13" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB13" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD13" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE13" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF13" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG13" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH13" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI13" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ13" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK13" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL13" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM13" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN13" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO13" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP13" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ13" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR13" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS13" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT13" s="20">
+        <f t="shared" ca="1" si="13"/>
+        <v>46084</v>
+      </c>
+      <c r="AU13" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD13" s="43" t="s">
+        <v>105</v>
       </c>
       <c r="BE13" s="15">
-        <v>9477896544</v>
+        <v>9577896583</v>
+      </c>
+      <c r="BF13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG13" s="43" t="s">
+        <v>106</v>
       </c>
       <c r="BH13" s="15">
-        <v>47678965289</v>
+        <v>49678965413</v>
+      </c>
+      <c r="BI13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ13" s="43" t="s">
+        <v>107</v>
       </c>
       <c r="BK13" s="15" t="s">
         <v>152</v>
       </c>
+      <c r="BL13" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM13" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN13" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO13" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP13" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ13" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR13" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS13" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT13" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU13" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV13" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW13" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX13" s="30" t="s">
+        <v>119</v>
+      </c>
     </row>
-    <row r="14" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="28"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K14" s="35">
+        <f t="shared" ca="1" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L14" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T14" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U14" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V14" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W14" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X14" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y14" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AC14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD14" s="40">
+        <v>766</v>
+      </c>
+      <c r="AE14" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF14" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG14" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH14" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI14" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ14" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK14" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL14" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM14" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN14" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO14" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP14" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="AQ14" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR14" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS14" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT14" s="20" t="str">
+        <f t="shared" si="13"/>
+        <v>N/A</v>
+      </c>
+      <c r="AU14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AV14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD14" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE14" s="15">
+        <v>9577896584</v>
+      </c>
+      <c r="BF14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG14" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH14" s="15">
+        <v>49678965414</v>
+      </c>
+      <c r="BI14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ14" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK14" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="BE14" s="15">
-        <v>9477896545</v>
-      </c>
-      <c r="BH14" s="15">
-        <v>47678965290</v>
-      </c>
-      <c r="BK14" s="15" t="s">
+      <c r="BL14" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM14" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN14" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="BO14" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="BP14" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ14" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR14" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS14" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT14" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU14" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV14" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW14" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX14" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="28"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="K15" s="35">
+        <f t="shared" ca="1" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L15" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="M15" s="30" t="s">
+        <v>79</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="O15" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="S15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="T15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="U15" s="37" t="s">
+        <v>84</v>
+      </c>
+      <c r="V15" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="W15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="X15" s="39">
+        <f t="shared" ca="1" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y15" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z15" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA15" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB15" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AC15" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD15" s="40">
+        <v>765</v>
+      </c>
+      <c r="AE15" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="AF15" s="16">
+        <v>40</v>
+      </c>
+      <c r="AG15" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH15" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI15" s="18">
+        <v>43831</v>
+      </c>
+      <c r="AJ15" s="18">
+        <v>45292</v>
+      </c>
+      <c r="AK15" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="AL15" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="AM15" s="18">
+        <f ca="1">TODAY()+365</f>
+        <v>46084</v>
+      </c>
+      <c r="AN15" s="34">
+        <v>110</v>
+      </c>
+      <c r="AO15" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="AP15" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ15" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR15" s="42">
+        <f t="shared" ca="1" si="15"/>
+        <v>45688</v>
+      </c>
+      <c r="AS15" s="42">
+        <f t="shared" ca="1" si="16"/>
+        <v>45688</v>
+      </c>
+      <c r="AT15" s="20">
+        <f t="shared" ca="1" si="13"/>
+        <v>46084</v>
+      </c>
+      <c r="AU15" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="AV15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AW15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AX15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AY15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AZ15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="BA15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BC15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD15" s="43" t="s">
+        <v>105</v>
+      </c>
+      <c r="BE15" s="15">
+        <v>9577896585</v>
+      </c>
+      <c r="BF15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG15" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="BH15" s="15">
+        <v>49678965415</v>
+      </c>
+      <c r="BI15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="BJ15" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="BK15" s="15" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="15" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
-        <v>155</v>
-      </c>
-      <c r="BE15" s="15">
-        <v>9477896546</v>
-      </c>
-      <c r="BH15" s="15">
-        <v>47678965291</v>
-      </c>
-      <c r="BK15" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="16" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="BE16" s="15">
-        <v>9477896547</v>
-      </c>
-      <c r="BH16" s="15">
-        <v>47678965292</v>
-      </c>
-      <c r="BK16" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="BE17" s="15">
-        <v>9477896548</v>
-      </c>
-      <c r="BH17" s="15">
-        <v>47678965293</v>
-      </c>
-      <c r="BK17" s="15" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="BE18" s="15">
-        <v>9477896549</v>
-      </c>
-      <c r="BH18" s="15">
-        <v>47678965294</v>
-      </c>
-      <c r="BK18" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="19" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="BE19" s="15">
-        <v>9477896550</v>
-      </c>
-      <c r="BH19" s="15">
-        <v>47678965295</v>
-      </c>
-      <c r="BK19" s="15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
-        <v>165</v>
-      </c>
-      <c r="BE20" s="15">
-        <v>9477896551</v>
-      </c>
-      <c r="BH20" s="15">
-        <v>47678965296</v>
-      </c>
-      <c r="BK20" s="15" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:63" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="BE21" s="15">
-        <v>9477896552</v>
-      </c>
-      <c r="BH21" s="15">
-        <v>47678965297</v>
-      </c>
-      <c r="BK21" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="22" ht="14.5" customHeight="1" spans="57:57" x14ac:dyDescent="0.25">
-      <c r="BE22" s="15">
-        <v>9477896553</v>
-      </c>
-    </row>
-    <row r="23" ht="14.5" customHeight="1" spans="57:57" x14ac:dyDescent="0.25">
-      <c r="BE23" s="15">
-        <v>9477896554</v>
+      <c r="BL15" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM15" s="44">
+        <v>35591</v>
+      </c>
+      <c r="BN15" s="45" t="s">
+        <v>127</v>
+      </c>
+      <c r="BO15" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="BP15" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="BQ15" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="BR15" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="BS15" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="BT15" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="BU15" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BV15" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BW15" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX15" s="30" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/testDataPoland5.xlsx
+++ b/Data/testDataPoland5.xlsx
@@ -1,35 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{6BE09BF7-166C-4551-A9A0-75E7F910E6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="197">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -253,12 +238,27 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Darian Mayer' Employee:{undefined}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>766 Recruitment (Gybop Sytavu (10223416))</t>
   </si>
   <si>
     <t>Poland</t>
   </si>
   <si>
+    <t>Darian</t>
+  </si>
+  <si>
+    <t>Mayer</t>
+  </si>
+  <si>
     <t xml:space="preserve">698 980 460 </t>
   </si>
   <si>
@@ -355,6 +355,9 @@
     <t>ID Card</t>
   </si>
   <si>
+    <t>GSK476930</t>
+  </si>
+  <si>
     <t>Male</t>
   </si>
   <si>
@@ -394,9 +397,408 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Tommie Abshire' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   performing click action[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
     <t>765 Store Management (Kires Pivyba (10226524))</t>
   </si>
   <si>
+    <t>Tommie</t>
+  </si>
+  <si>
+    <t>Abshire</t>
+  </si>
+  <si>
     <t>Auto 91546437</t>
   </si>
   <si>
@@ -412,85 +814,2543 @@
     <t xml:space="preserve">251 Management Retail </t>
   </si>
   <si>
+    <t>GSK476931</t>
+  </si>
+  <si>
     <t>Single (Poland)</t>
   </si>
   <si>
     <t>Test_3</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Christine Lebsack' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Christine</t>
+  </si>
+  <si>
+    <t>Lebsack</t>
+  </si>
+  <si>
+    <t>GSK476932</t>
+  </si>
+  <si>
     <t>Test_4</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Kody Friesen' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   performing click action[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Kody</t>
+  </si>
+  <si>
+    <t>Friesen</t>
+  </si>
+  <si>
     <t>Auto 14500870</t>
   </si>
   <si>
+    <t>GSK476933</t>
+  </si>
+  <si>
     <t>Test_5</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Margaret Casper' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Margaret</t>
+  </si>
+  <si>
+    <t>Casper</t>
+  </si>
+  <si>
+    <t>GSK476934</t>
+  </si>
+  <si>
     <t>Test_6</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Alyson Anderson' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   performing click action[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Alyson</t>
+  </si>
+  <si>
+    <t>Anderson</t>
+  </si>
+  <si>
+    <t>GSK476935</t>
+  </si>
+  <si>
     <t>Test_7</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Sterling Christiansen' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Sterling</t>
+  </si>
+  <si>
+    <t>Christiansen</t>
+  </si>
+  <si>
+    <t>GSK476936</t>
+  </si>
+  <si>
     <t>Test_8</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Francisca Kris' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   performing click action[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Francisca</t>
+  </si>
+  <si>
+    <t>Kris</t>
+  </si>
+  <si>
+    <t>GSK476937</t>
+  </si>
+  <si>
     <t>Test_9</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Forrest Kertzmann' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Forrest</t>
+  </si>
+  <si>
+    <t>Kertzmann</t>
+  </si>
+  <si>
+    <t>GSK476938</t>
+  </si>
+  <si>
     <t>Test_10</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Uriah O'Kon' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   performing click action[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Uriah</t>
+  </si>
+  <si>
+    <t>O'Kon</t>
+  </si>
+  <si>
+    <t>GSK476939</t>
+  </si>
+  <si>
     <t>Test_11</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Marcellus O'Conner' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Marcellus</t>
+  </si>
+  <si>
+    <t>O'Conner</t>
+  </si>
+  <si>
+    <t>GSK476940</t>
+  </si>
+  <si>
     <t>Test_12</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Shanny Lindgren' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Shanny</t>
+  </si>
+  <si>
+    <t>Lindgren</t>
+  </si>
+  <si>
+    <t>GSK476941</t>
+  </si>
+  <si>
     <t>Test_13</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Buster Klocko' Employee:{}TimeoutError: locator.focus: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('Position Request Reason')[22m
+</t>
+  </si>
+  <si>
+    <t>Buster</t>
+  </si>
+  <si>
+    <t>Klocko</t>
+  </si>
+  <si>
+    <t>GSK476942</t>
+  </si>
+  <si>
     <t>Test_14</t>
   </si>
   <si>
-    <t>GSK476930</t>
-  </si>
-  <si>
-    <t>GSK476931</t>
-  </si>
-  <si>
-    <t>GSK476932</t>
-  </si>
-  <si>
-    <t>GSK476933</t>
-  </si>
-  <si>
-    <t>GSK476934</t>
-  </si>
-  <si>
-    <t>GSK476935</t>
-  </si>
-  <si>
-    <t>GSK476936</t>
-  </si>
-  <si>
-    <t>GSK476937</t>
-  </si>
-  <si>
-    <t>GSK476938</t>
-  </si>
-  <si>
-    <t>GSK476939</t>
-  </si>
-  <si>
-    <t>GSK476940</t>
-  </si>
-  <si>
-    <t>GSK476941</t>
-  </si>
-  <si>
-    <t>GSK476942</t>
+    <t xml:space="preserve">Test failed for 'Aditya Mayer' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//*[@data-automation-label=\'Full time\' or text()=\'Full time\'])[1]')[22m
+[2m  -   locator resolved to &lt;p data-automation-id="promptOption" data-automatio…&gt;Full time&lt;/p&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div data-automation-id="promptOption" class="css-svf…&gt;Locations by Location Hierarchy&lt;/div&gt; from &lt;div data-popup-type="ck" data-popup-version="2" clas…&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Aditya</t>
   </si>
   <si>
     <t>GSK476943</t>
@@ -499,105 +3359,99 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <color indexed="63"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color indexed="63"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color indexed="12"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color indexed="12"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color indexed="8"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color indexed="10"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color indexed="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -609,7 +3463,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -626,7 +3480,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -640,18 +3494,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -661,12 +3507,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -1104,9 +3946,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BX15"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
     <col min="2" max="2" width="34.1796875" customWidth="1"/>
@@ -1171,7 +4013,7 @@
     <col min="76" max="76" width="26.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76" s="2" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" ht="14.5" customHeight="1" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1401,87 +4243,95 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="1"/>
+      <c r="B2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D2" s="29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>79</v>
+      </c>
       <c r="H2" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I2" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="35">
+        <f t="shared" ref="K2:K14" si="0">TODAY()-31</f>
+        <v>45688</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J2" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="35">
-        <f t="shared" ref="K2:K14" ca="1" si="0">TODAY()-31</f>
+      <c r="M2" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R2" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S2" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V2" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X2" s="39">
+        <f t="shared" ref="X2" si="1">K2</f>
         <v>45688</v>
       </c>
-      <c r="L2" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O2" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P2" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q2" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R2" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S2" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T2" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U2" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V2" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W2" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X2" s="39">
-        <f t="shared" ref="X2" ca="1" si="1">K2</f>
-        <v>45688</v>
-      </c>
       <c r="Y2" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AB2" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AC2" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD2" s="40">
         <v>766</v>
@@ -1493,10 +4343,10 @@
         <v>40</v>
       </c>
       <c r="AG2" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH2" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI2" s="18">
         <v>43831</v>
@@ -1505,210 +4355,218 @@
         <v>45292</v>
       </c>
       <c r="AK2" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL2" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="34">
         <v>110</v>
       </c>
       <c r="AO2" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP2" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ2" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR2" s="42">
-        <f t="shared" ref="AR2" ca="1" si="2">X2</f>
+        <f t="shared" ref="AR2" si="2">X2</f>
         <v>45688</v>
       </c>
       <c r="AS2" s="42">
-        <f t="shared" ref="AS2" ca="1" si="3">X2</f>
+        <f t="shared" ref="AS2" si="3">X2</f>
         <v>45688</v>
       </c>
-      <c r="AT2" s="20" t="str">
+      <c r="AT2" s="20">
         <f t="shared" ref="AT2:AT3" si="4">AM2</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU2" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD2" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE2" s="15">
         <v>9577896572</v>
       </c>
       <c r="BF2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG2" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH2" s="15">
         <v>49678965402</v>
       </c>
       <c r="BI2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ2" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK2" s="15" t="s">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="BL2" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM2" s="44">
         <v>35591</v>
       </c>
       <c r="BN2" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO2" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP2" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ2" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR2" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS2" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT2" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU2" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV2" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW2" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX2" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="1"/>
+        <v>125</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D3" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>129</v>
+      </c>
       <c r="H3" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I3" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" s="35">
+        <f t="shared" ref="K3:K15" si="5">TODAY()-31</f>
+        <v>45688</v>
+      </c>
+      <c r="L3" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J3" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K3" s="35">
-        <f t="shared" ref="K3:K15" ca="1" si="5">TODAY()-31</f>
+      <c r="M3" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R3" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S3" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V3" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W3" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X3" s="39">
+        <f t="shared" ref="X3:X4" si="6">K3</f>
         <v>45688</v>
       </c>
-      <c r="L3" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N3" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O3" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q3" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R3" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T3" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U3" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V3" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W3" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X3" s="39">
-        <f t="shared" ref="X3:X4" ca="1" si="6">K3</f>
-        <v>45688</v>
-      </c>
       <c r="Y3" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC3" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD3" s="40">
         <v>765</v>
@@ -1720,10 +4578,10 @@
         <v>40</v>
       </c>
       <c r="AG3" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH3" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI3" s="18">
         <v>43831</v>
@@ -1732,211 +4590,219 @@
         <v>45292</v>
       </c>
       <c r="AK3" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL3" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM3" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN3" s="34">
         <v>110</v>
       </c>
       <c r="AO3" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP3" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ3" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR3" s="42">
-        <f t="shared" ref="AR3:AR4" ca="1" si="7">X3</f>
+        <f t="shared" ref="AR3:AR4" si="7">X3</f>
         <v>45688</v>
       </c>
       <c r="AS3" s="42">
-        <f t="shared" ref="AS3:AS4" ca="1" si="8">X3</f>
+        <f t="shared" ref="AS3:AS4" si="8">X3</f>
         <v>45688</v>
       </c>
       <c r="AT3" s="20">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>46084</v>
       </c>
       <c r="AU3" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV3" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX3" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD3" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE3" s="15">
         <v>9577896573</v>
       </c>
       <c r="BF3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG3" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH3" s="15">
         <v>49678965403</v>
       </c>
       <c r="BI3" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ3" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK3" s="15" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="BL3" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM3" s="44">
         <v>35591</v>
       </c>
       <c r="BN3" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO3" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP3" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR3" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS3" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT3" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU3" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV3" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW3" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX3" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K4" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L4" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N4" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P4" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q4" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R4" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S4" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T4" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U4" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V4" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W4" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X4" s="39">
+        <f t="shared" si="6"/>
+        <v>45688</v>
+      </c>
+      <c r="Y4" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC4" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP3" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ3" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR3" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS3" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT3" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU3" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV3" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW3" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX3" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L4" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N4" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O4" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P4" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q4" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R4" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S4" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T4" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U4" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V4" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X4" s="39">
-        <f t="shared" ca="1" si="6"/>
-        <v>45688</v>
-      </c>
-      <c r="Y4" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB4" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC4" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD4" s="40">
         <v>766</v>
@@ -1948,10 +4814,10 @@
         <v>40</v>
       </c>
       <c r="AG4" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI4" s="18">
         <v>43831</v>
@@ -1960,210 +4826,218 @@
         <v>45292</v>
       </c>
       <c r="AK4" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL4" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM4" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN4" s="34">
         <v>110</v>
       </c>
       <c r="AO4" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP4" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ4" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR4" s="42">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" si="7"/>
         <v>45688</v>
       </c>
       <c r="AS4" s="42">
-        <f t="shared" ca="1" si="8"/>
+        <f t="shared" si="8"/>
         <v>45688</v>
       </c>
-      <c r="AT4" s="20" t="str">
+      <c r="AT4" s="20">
         <f t="shared" ref="AT4:AT5" si="9">AM4</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU4" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV4" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW4" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX4" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY4" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ4" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA4" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB4" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD4" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE4" s="15">
         <v>9577896574</v>
       </c>
       <c r="BF4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG4" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH4" s="15">
         <v>49678965404</v>
       </c>
       <c r="BI4" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ4" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK4" s="15" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="BL4" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM4" s="44">
         <v>35591</v>
       </c>
       <c r="BN4" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO4" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP4" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ4" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR4" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS4" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT4" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU4" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV4" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW4" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX4" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A5" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="1"/>
+        <v>142</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D5" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>145</v>
+      </c>
       <c r="H5" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I5" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K5" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L5" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="35">
-        <f t="shared" ca="1" si="5"/>
+      <c r="M5" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P5" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q5" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R5" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S5" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U5" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V5" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X5" s="39">
+        <f t="shared" ref="X5:X6" si="10">K5</f>
         <v>45688</v>
       </c>
-      <c r="L5" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M5" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N5" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P5" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q5" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R5" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S5" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T5" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U5" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V5" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X5" s="39">
-        <f t="shared" ref="X5:X6" ca="1" si="10">K5</f>
-        <v>45688</v>
-      </c>
       <c r="Y5" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB5" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC5" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD5" s="40">
         <v>765</v>
@@ -2175,10 +5049,10 @@
         <v>40</v>
       </c>
       <c r="AG5" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI5" s="18">
         <v>43831</v>
@@ -2187,211 +5061,219 @@
         <v>45292</v>
       </c>
       <c r="AK5" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL5" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM5" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN5" s="34">
         <v>110</v>
       </c>
       <c r="AO5" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP5" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ5" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR5" s="42">
-        <f t="shared" ref="AR5:AR6" ca="1" si="11">X5</f>
+        <f t="shared" ref="AR5:AR6" si="11">X5</f>
         <v>45688</v>
       </c>
       <c r="AS5" s="42">
-        <f t="shared" ref="AS5:AS6" ca="1" si="12">X5</f>
+        <f t="shared" ref="AS5:AS6" si="12">X5</f>
         <v>45688</v>
       </c>
       <c r="AT5" s="20">
-        <f t="shared" ca="1" si="9"/>
+        <f t="shared" si="9"/>
         <v>46084</v>
       </c>
       <c r="AU5" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV5" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW5" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX5" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY5" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ5" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA5" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB5" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD5" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE5" s="15">
         <v>9577896575</v>
       </c>
       <c r="BF5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG5" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH5" s="15">
         <v>49678965405</v>
       </c>
       <c r="BI5" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ5" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK5" s="15" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="BL5" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM5" s="44">
         <v>35591</v>
       </c>
       <c r="BN5" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO5" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP5" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ5" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR5" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS5" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT5" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU5" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV5" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW5" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX5" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K6" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O6" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S6" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U6" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X6" s="39">
+        <f t="shared" si="10"/>
+        <v>45688</v>
+      </c>
+      <c r="Y6" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC6" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP5" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ5" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR5" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS5" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT5" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU5" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV5" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW5" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX5" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K6" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L6" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M6" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O6" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R6" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S6" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U6" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V6" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X6" s="39">
-        <f t="shared" ca="1" si="10"/>
-        <v>45688</v>
-      </c>
-      <c r="Y6" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z6" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA6" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC6" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD6" s="40">
         <v>766</v>
@@ -2403,10 +5285,10 @@
         <v>40</v>
       </c>
       <c r="AG6" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH6" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI6" s="18">
         <v>43831</v>
@@ -2415,210 +5297,218 @@
         <v>45292</v>
       </c>
       <c r="AK6" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL6" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM6" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN6" s="34">
         <v>110</v>
       </c>
       <c r="AO6" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP6" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ6" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR6" s="42">
-        <f t="shared" ca="1" si="11"/>
+        <f t="shared" si="11"/>
         <v>45688</v>
       </c>
       <c r="AS6" s="42">
-        <f t="shared" ca="1" si="12"/>
+        <f t="shared" si="12"/>
         <v>45688</v>
       </c>
-      <c r="AT6" s="20" t="str">
+      <c r="AT6" s="20">
         <f t="shared" ref="AT6:AT15" si="13">AM6</f>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU6" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV6" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW6" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX6" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY6" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ6" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA6" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB6" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD6" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE6" s="15">
         <v>9577896576</v>
       </c>
       <c r="BF6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG6" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH6" s="15">
         <v>49678965406</v>
       </c>
       <c r="BI6" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ6" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK6" s="15" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="BL6" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM6" s="44">
         <v>35591</v>
       </c>
       <c r="BN6" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO6" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP6" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ6" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR6" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS6" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT6" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU6" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV6" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW6" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX6" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K7" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L7" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N7" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O7" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P7" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q7" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R7" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S7" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U7" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V7" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X7" s="39">
+        <f t="shared" ref="X7:X15" si="14">K7</f>
+        <v>45688</v>
+      </c>
+      <c r="Y7" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA7" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB7" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J7" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K7" s="35">
-        <f t="shared" ca="1" si="5"/>
-        <v>45688</v>
-      </c>
-      <c r="L7" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N7" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O7" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q7" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R7" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S7" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T7" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U7" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V7" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X7" s="39">
-        <f t="shared" ref="X7:X15" ca="1" si="14">K7</f>
-        <v>45688</v>
-      </c>
-      <c r="Y7" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA7" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="AC7" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD7" s="40">
         <v>765</v>
@@ -2630,10 +5520,10 @@
         <v>40</v>
       </c>
       <c r="AG7" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH7" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI7" s="18">
         <v>43831</v>
@@ -2642,211 +5532,219 @@
         <v>45292</v>
       </c>
       <c r="AK7" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL7" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM7" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN7" s="34">
         <v>110</v>
       </c>
       <c r="AO7" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP7" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ7" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR7" s="42">
-        <f t="shared" ref="AR7:AR15" ca="1" si="15">X7</f>
+        <f t="shared" ref="AR7:AR15" si="15">X7</f>
         <v>45688</v>
       </c>
       <c r="AS7" s="42">
-        <f t="shared" ref="AS7:AS15" ca="1" si="16">X7</f>
+        <f t="shared" ref="AS7:AS15" si="16">X7</f>
         <v>45688</v>
       </c>
       <c r="AT7" s="20">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>46084</v>
       </c>
       <c r="AU7" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV7" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW7" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX7" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY7" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ7" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA7" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB7" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD7" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE7" s="15">
         <v>9577896577</v>
       </c>
       <c r="BF7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG7" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH7" s="15">
         <v>49678965407</v>
       </c>
       <c r="BI7" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ7" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK7" s="15" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="BL7" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM7" s="44">
         <v>35591</v>
       </c>
       <c r="BN7" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO7" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ7" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR7" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS7" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT7" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU7" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV7" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW7" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX7" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A8" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L8" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O8" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U8" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V8" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X8" s="39">
+        <f t="shared" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y8" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC8" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP7" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ7" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR7" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS7" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT7" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU7" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV7" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW7" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX7" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L8" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O8" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P8" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V8" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X8" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
-      <c r="Y8" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z8" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA8" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB8" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC8" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD8" s="40">
         <v>766</v>
@@ -2858,10 +5756,10 @@
         <v>40</v>
       </c>
       <c r="AG8" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH8" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI8" s="18">
         <v>43831</v>
@@ -2870,210 +5768,218 @@
         <v>45292</v>
       </c>
       <c r="AK8" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL8" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM8" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN8" s="34">
         <v>110</v>
       </c>
       <c r="AO8" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP8" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ8" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR8" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS8" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
-      <c r="AT8" s="20" t="str">
+      <c r="AT8" s="20">
         <f t="shared" si="13"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU8" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV8" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW8" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX8" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY8" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ8" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA8" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB8" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD8" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE8" s="15">
         <v>9577896578</v>
       </c>
       <c r="BF8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG8" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH8" s="15">
         <v>49678965408</v>
       </c>
       <c r="BI8" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ8" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK8" s="15" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="BL8" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM8" s="44">
         <v>35591</v>
       </c>
       <c r="BN8" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO8" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP8" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ8" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR8" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS8" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT8" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU8" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV8" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW8" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX8" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A9" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="1"/>
+        <v>163</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D9" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E9" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>166</v>
+      </c>
       <c r="H9" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I9" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L9" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K9" s="35">
-        <f t="shared" ca="1" si="5"/>
+      <c r="M9" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P9" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R9" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S9" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U9" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V9" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X9" s="39">
+        <f t="shared" si="14"/>
         <v>45688</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N9" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O9" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q9" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R9" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U9" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V9" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W9" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X9" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
       <c r="Y9" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB9" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC9" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="40">
         <v>765</v>
@@ -3085,10 +5991,10 @@
         <v>40</v>
       </c>
       <c r="AG9" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH9" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI9" s="18">
         <v>43831</v>
@@ -3097,211 +6003,219 @@
         <v>45292</v>
       </c>
       <c r="AK9" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL9" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM9" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN9" s="34">
         <v>110</v>
       </c>
       <c r="AO9" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP9" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ9" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR9" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS9" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
       <c r="AT9" s="20">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>46084</v>
       </c>
       <c r="AU9" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV9" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW9" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX9" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY9" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ9" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA9" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB9" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD9" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE9" s="15">
         <v>9577896579</v>
       </c>
       <c r="BF9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG9" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH9" s="15">
         <v>49678965409</v>
       </c>
       <c r="BI9" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ9" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK9" s="15" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="BL9" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM9" s="44">
         <v>35591</v>
       </c>
       <c r="BN9" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO9" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP9" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ9" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR9" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS9" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT9" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU9" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV9" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW9" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX9" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L10" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O10" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R10" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U10" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V10" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X10" s="39">
+        <f t="shared" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y10" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA10" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC10" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP9" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ9" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR9" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS9" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT9" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU9" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV9" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW9" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX9" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L10" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M10" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N10" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O10" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q10" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R10" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T10" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U10" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V10" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W10" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X10" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
-      <c r="Y10" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC10" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD10" s="40">
         <v>766</v>
@@ -3313,10 +6227,10 @@
         <v>40</v>
       </c>
       <c r="AG10" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH10" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI10" s="18">
         <v>43831</v>
@@ -3325,210 +6239,218 @@
         <v>45292</v>
       </c>
       <c r="AK10" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL10" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM10" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN10" s="34">
         <v>110</v>
       </c>
       <c r="AO10" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP10" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ10" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR10" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS10" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
-      <c r="AT10" s="20" t="str">
+      <c r="AT10" s="20">
         <f t="shared" si="13"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU10" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV10" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW10" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX10" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY10" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ10" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA10" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB10" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD10" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE10" s="15">
         <v>9577896580</v>
       </c>
       <c r="BF10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG10" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH10" s="15">
         <v>49678965410</v>
       </c>
       <c r="BI10" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ10" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK10" s="15" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="BL10" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM10" s="44">
         <v>35591</v>
       </c>
       <c r="BN10" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO10" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP10" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ10" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR10" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS10" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT10" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU10" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV10" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW10" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX10" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="1"/>
+        <v>173</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D11" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E11" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>176</v>
+      </c>
       <c r="H11" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I11" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L11" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K11" s="35">
-        <f t="shared" ca="1" si="5"/>
+      <c r="M11" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P11" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q11" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R11" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S11" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U11" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V11" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W11" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X11" s="39">
+        <f t="shared" si="14"/>
         <v>45688</v>
       </c>
-      <c r="L11" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O11" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q11" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R11" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S11" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T11" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U11" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V11" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W11" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X11" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
       <c r="Y11" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB11" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC11" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD11" s="40">
         <v>765</v>
@@ -3540,10 +6462,10 @@
         <v>40</v>
       </c>
       <c r="AG11" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH11" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI11" s="18">
         <v>43831</v>
@@ -3552,211 +6474,219 @@
         <v>45292</v>
       </c>
       <c r="AK11" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL11" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM11" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN11" s="34">
         <v>110</v>
       </c>
       <c r="AO11" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP11" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ11" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR11" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS11" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
       <c r="AT11" s="20">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>46084</v>
       </c>
       <c r="AU11" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV11" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW11" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX11" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY11" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ11" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA11" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB11" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD11" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE11" s="15">
         <v>9577896581</v>
       </c>
       <c r="BF11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG11" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH11" s="15">
         <v>49678965411</v>
       </c>
       <c r="BI11" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ11" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK11" s="15" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="BL11" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM11" s="44">
         <v>35591</v>
       </c>
       <c r="BN11" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO11" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP11" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ11" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR11" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS11" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT11" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU11" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV11" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW11" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX11" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A12" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K12" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L12" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P12" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R12" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S12" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U12" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V12" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W12" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X12" s="39">
+        <f t="shared" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y12" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC12" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP11" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ11" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR11" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS11" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT11" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU11" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV11" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW11" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX11" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J12" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M12" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N12" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O12" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P12" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q12" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R12" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S12" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T12" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U12" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V12" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W12" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X12" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
-      <c r="Y12" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z12" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA12" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC12" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD12" s="40">
         <v>766</v>
@@ -3768,10 +6698,10 @@
         <v>40</v>
       </c>
       <c r="AG12" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH12" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI12" s="18">
         <v>43831</v>
@@ -3780,210 +6710,218 @@
         <v>45292</v>
       </c>
       <c r="AK12" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL12" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM12" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN12" s="34">
         <v>110</v>
       </c>
       <c r="AO12" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP12" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ12" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR12" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS12" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
-      <c r="AT12" s="20" t="str">
+      <c r="AT12" s="20">
         <f t="shared" si="13"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU12" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV12" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW12" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX12" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY12" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ12" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA12" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB12" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD12" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE12" s="15">
         <v>9577896582</v>
       </c>
       <c r="BF12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG12" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH12" s="15">
         <v>49678965412</v>
       </c>
       <c r="BI12" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ12" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK12" s="15" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="BL12" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM12" s="44">
         <v>35591</v>
       </c>
       <c r="BN12" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO12" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP12" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ12" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR12" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS12" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT12" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU12" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV12" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW12" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX12" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A13" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="1"/>
+        <v>183</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D13" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>186</v>
+      </c>
       <c r="H13" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I13" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K13" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J13" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" s="35">
-        <f t="shared" ca="1" si="5"/>
+      <c r="M13" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N13" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O13" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q13" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R13" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S13" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U13" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V13" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X13" s="39">
+        <f t="shared" si="14"/>
         <v>45688</v>
       </c>
-      <c r="L13" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M13" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N13" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O13" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P13" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q13" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R13" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S13" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T13" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U13" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V13" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W13" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X13" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
       <c r="Y13" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AA13" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB13" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC13" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD13" s="40">
         <v>765</v>
@@ -3995,10 +6933,10 @@
         <v>40</v>
       </c>
       <c r="AG13" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH13" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI13" s="18">
         <v>43831</v>
@@ -4007,211 +6945,219 @@
         <v>45292</v>
       </c>
       <c r="AK13" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL13" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM13" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN13" s="34">
         <v>110</v>
       </c>
       <c r="AO13" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP13" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ13" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR13" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS13" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
       <c r="AT13" s="20">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>46084</v>
       </c>
       <c r="AU13" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV13" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW13" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX13" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY13" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ13" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA13" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB13" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD13" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE13" s="15">
         <v>9577896583</v>
       </c>
       <c r="BF13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG13" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH13" s="15">
         <v>49678965413</v>
       </c>
       <c r="BI13" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ13" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK13" s="15" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="BL13" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM13" s="44">
         <v>35591</v>
       </c>
       <c r="BN13" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO13" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="BP13" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="BQ13" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR13" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS13" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="BT13" s="46" t="s">
+        <v>120</v>
+      </c>
+      <c r="BU13" s="46" t="s">
+        <v>121</v>
+      </c>
+      <c r="BV13" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="BW13" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX13" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="A14" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K14" s="35">
+        <f t="shared" si="0"/>
+        <v>45688</v>
+      </c>
+      <c r="L14" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O14" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P14" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q14" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S14" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U14" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V14" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W14" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="39">
+        <f t="shared" si="14"/>
+        <v>45688</v>
+      </c>
+      <c r="Y14" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC14" s="14" t="s">
         <v>94</v>
-      </c>
-      <c r="BP13" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="BQ13" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="BR13" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="BS13" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="BT13" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="BU13" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="BV13" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="BW13" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="BX13" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K14" s="35">
-        <f t="shared" ca="1" si="0"/>
-        <v>45688</v>
-      </c>
-      <c r="L14" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M14" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N14" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O14" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P14" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q14" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R14" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S14" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T14" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U14" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V14" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W14" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X14" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
-      <c r="Y14" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z14" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA14" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AB14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC14" s="14" t="s">
-        <v>90</v>
       </c>
       <c r="AD14" s="40">
         <v>766</v>
@@ -4223,10 +7169,10 @@
         <v>40</v>
       </c>
       <c r="AG14" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH14" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI14" s="18">
         <v>43831</v>
@@ -4235,210 +7181,218 @@
         <v>45292</v>
       </c>
       <c r="AK14" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL14" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM14" s="18" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AN14" s="34">
         <v>110</v>
       </c>
       <c r="AO14" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP14" s="14" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AQ14" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR14" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS14" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
-      <c r="AT14" s="20" t="str">
+      <c r="AT14" s="20">
         <f t="shared" si="13"/>
-        <v>N/A</v>
+        <v>NaN</v>
       </c>
       <c r="AU14" s="6" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AV14" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AW14" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX14" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY14" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ14" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA14" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB14" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD14" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE14" s="15">
         <v>9577896584</v>
       </c>
       <c r="BF14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG14" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH14" s="15">
         <v>49678965414</v>
       </c>
       <c r="BI14" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ14" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK14" s="15" t="s">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="BL14" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM14" s="44">
         <v>35591</v>
       </c>
       <c r="BN14" s="45" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="BO14" s="24" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="BP14" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ14" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR14" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS14" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT14" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU14" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV14" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW14" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX14" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:76" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="14.5" customHeight="1" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A15" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="1"/>
+        <v>193</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="D15" s="29" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E15" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
+        <v>77</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>79</v>
+      </c>
       <c r="H15" s="33" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I15" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="35">
+        <f t="shared" si="5"/>
+        <v>45688</v>
+      </c>
+      <c r="L15" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="J15" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" s="35">
-        <f t="shared" ca="1" si="5"/>
+      <c r="M15" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="O15" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="P15" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="R15" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="S15" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="T15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="U15" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="V15" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="W15" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="X15" s="39">
+        <f t="shared" si="14"/>
         <v>45688</v>
       </c>
-      <c r="L15" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="M15" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="N15" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="O15" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="P15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q15" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="R15" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="S15" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="T15" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="V15" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="W15" s="34" t="s">
-        <v>78</v>
-      </c>
-      <c r="X15" s="39">
-        <f t="shared" ca="1" si="14"/>
-        <v>45688</v>
-      </c>
       <c r="Y15" s="34" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="AA15" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AB15" s="6" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="AC15" s="14" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD15" s="40">
         <v>765</v>
@@ -4450,10 +7404,10 @@
         <v>40</v>
       </c>
       <c r="AG15" s="41" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AH15" s="41" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AI15" s="18">
         <v>43831</v>
@@ -4462,133 +7416,132 @@
         <v>45292</v>
       </c>
       <c r="AK15" s="17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AL15" s="17" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM15" s="18">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46084</v>
       </c>
       <c r="AN15" s="34">
         <v>110</v>
       </c>
       <c r="AO15" s="34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AP15" s="14" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AQ15" s="34" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AR15" s="42">
-        <f t="shared" ca="1" si="15"/>
+        <f t="shared" si="15"/>
         <v>45688</v>
       </c>
       <c r="AS15" s="42">
-        <f t="shared" ca="1" si="16"/>
+        <f t="shared" si="16"/>
         <v>45688</v>
       </c>
       <c r="AT15" s="20">
-        <f t="shared" ca="1" si="13"/>
+        <f t="shared" si="13"/>
         <v>46084</v>
       </c>
       <c r="AU15" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV15" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AW15" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AX15" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AY15" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AZ15" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="BA15" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="BB15" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BC15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BD15" s="43" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="BE15" s="15">
         <v>9577896585</v>
       </c>
       <c r="BF15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BG15" s="43" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BH15" s="15">
         <v>49678965415</v>
       </c>
       <c r="BI15" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BJ15" s="43" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="BK15" s="15" t="s">
-        <v>154</v>
+        <v>196</v>
       </c>
       <c r="BL15" s="14" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="BM15" s="44">
         <v>35591</v>
       </c>
       <c r="BN15" s="45" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="BO15" s="24" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="BP15" s="46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="BQ15" s="30" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BR15" s="47" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="BS15" s="30" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="BT15" s="46" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="BU15" s="46" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="BV15" s="30" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="BW15" s="30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="BX15" s="30" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>